--- a/test_notebooks_R/print_excel_05_05_2022.xlsx
+++ b/test_notebooks_R/print_excel_05_05_2022.xlsx
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B873"/>
     </row>
-    <row r="874">
+    <row r="874" ht="24" customHeight="1">
       <c r="A874"/>
       <c r="B874"/>
     </row>
